--- a/Input/DB_Portafolio Fruver.xlsx
+++ b/Input/DB_Portafolio Fruver.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prestamo\Documents\Isimo\Proyectos\Distribucion de Fruver\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F140389-0634-4E52-B5CB-734A563DB5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF20D08-1DDF-41F9-A8EB-008BFB461C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{64361134-23D5-B04D-A46F-A7C82A36887F}"/>
   </bookViews>

--- a/Input/DB_Portafolio Fruver.xlsx
+++ b/Input/DB_Portafolio Fruver.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prestamo\Documents\Isimo\Proyectos\Distribucion de Fruver\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF20D08-1DDF-41F9-A8EB-008BFB461C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE65CFEB-EDCD-4C76-B300-0CABB9CD806E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{64361134-23D5-B04D-A46F-A7C82A36887F}"/>
   </bookViews>
